--- a/Assignmnet-1/testplan.xlsx
+++ b/Assignmnet-1/testplan.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29113"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29108"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5F14F433-F2A0-410C-921A-99E83B68331A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{26DAB415-8564-4565-98A4-D4CD7DCB3EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="137">
   <si>
     <t>Test Plan</t>
   </si>
@@ -74,7 +74,7 @@
   </si>
   <si>
     <t>1. Navigate to the log in tab of any service 
-2. Enter data as specified 
+2. Enter data as specified credentials
 3. Click the Login button</t>
   </si>
   <si>
@@ -89,6 +89,38 @@
   </si>
   <si>
     <t>Passed</t>
+  </si>
+  <si>
+    <t>Validate Login</t>
+  </si>
+  <si>
+    <t>1. Navigate to the log in tab of any service 
+2. Enter valid credentials
+3. Click the Login button</t>
+  </si>
+  <si>
+    <t>User name: Ahmad_mohammad
+Password: 123456</t>
+  </si>
+  <si>
+    <t>User is able to log in successfully</t>
+  </si>
+  <si>
+    <t>User is logged in</t>
+  </si>
+  <si>
+    <t>Validate Login fails with empty fields</t>
+  </si>
+  <si>
+    <t>1. Navigate to the log in tab of any service 
+2. leave empty fields
+3. Click the Login button</t>
+  </si>
+  <si>
+    <t>User can't login to the service and a "All fields are required" error message displayed</t>
+  </si>
+  <si>
+    <t>User can't login and the error message displayed</t>
   </si>
   <si>
     <t>Validate login fails with wrong credentials</t>
@@ -99,47 +131,7 @@
 3. Click the Login button</t>
   </si>
   <si>
-    <t>Username: Ahmad_mohammad
-Password: Wrong123</t>
-  </si>
-  <si>
     <t>User can't login to the service and a "Wrong username or password" error message displayed</t>
-  </si>
-  <si>
-    <t>User can't login and the error message displayed</t>
-  </si>
-  <si>
-    <t>Validate Login fails with empty fields</t>
-  </si>
-  <si>
-    <t>1. Navigate to the log in tab of any service 
-2. leave empty fields
-3. Click the Login button</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Username: Ahmad_mohammad
-Password: </t>
-  </si>
-  <si>
-    <t>User can't login to the service and "All fields are required" error message displayed</t>
-  </si>
-  <si>
-    <t>Validate Login</t>
-  </si>
-  <si>
-    <t>1. Navigate to the log in tab of any service 
-2. Enter valid credentials
-3. Click the Login button</t>
-  </si>
-  <si>
-    <t>User name: Ahmad_mohammad
-Password: 123456</t>
-  </si>
-  <si>
-    <t>User is able to log in successfully</t>
-  </si>
-  <si>
-    <t>User is logged in</t>
   </si>
   <si>
     <t>Single Sign-On (SSO) feature</t>
@@ -446,7 +438,7 @@
     <t>delete/add user button is not visible</t>
   </si>
   <si>
-    <t>User is logged in as an viewer from any service</t>
+    <t>User is logged in as a viewer from any service</t>
   </si>
   <si>
     <t>Validate Viewer can use the services configs</t>
@@ -469,8 +461,7 @@
     <t>Validate Viewer can't edit services configs</t>
   </si>
   <si>
-    <t xml:space="preserve">1. Navigate to the Viewer tab
-</t>
+    <t>1. Navigate to the Viewer tab</t>
   </si>
   <si>
     <t>edit service button  is not visible in the viewer tab</t>
@@ -480,9 +471,6 @@
   </si>
   <si>
     <t>Validate Viewer can't manage users</t>
-  </si>
-  <si>
-    <t>1. Navigate to the Viewer tab</t>
   </si>
   <si>
     <t>delete/add user button is not visible in the viewer tab</t>
@@ -760,7 +748,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -842,57 +830,51 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -934,12 +916,6 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1295,28 +1271,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="35" t="s">
+      <c r="A1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="36"/>
-      <c r="C1" s="36"/>
-      <c r="D1" s="36"/>
-      <c r="E1" s="36"/>
-      <c r="F1" s="36"/>
-      <c r="G1" s="36"/>
-      <c r="H1" s="36"/>
-      <c r="I1" s="36"/>
+      <c r="B1" s="34"/>
+      <c r="C1" s="34"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
     </row>
     <row r="2" spans="1:9" ht="17.25" customHeight="1">
-      <c r="A2" s="36"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="36"/>
-      <c r="D2" s="36"/>
-      <c r="E2" s="36"/>
-      <c r="F2" s="36"/>
-      <c r="G2" s="36"/>
-      <c r="H2" s="36"/>
-      <c r="I2" s="36"/>
+      <c r="A2" s="34"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
     </row>
     <row r="3" spans="1:9" s="2" customFormat="1">
       <c r="A3" s="22" t="s">
@@ -1331,7 +1307,7 @@
       <c r="D3" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="25" t="s">
+      <c r="E3" s="28" t="s">
         <v>5</v>
       </c>
       <c r="F3" s="28" t="s">
@@ -1348,7 +1324,7 @@
       </c>
     </row>
     <row r="4" spans="1:9" ht="74.25" customHeight="1">
-      <c r="A4" s="45" t="s">
+      <c r="A4" s="43" t="s">
         <v>10</v>
       </c>
       <c r="B4" s="5" t="s">
@@ -1357,13 +1333,13 @@
       <c r="C4" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="30" t="s">
+      <c r="E4" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="29" t="s">
+      <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -1374,21 +1350,21 @@
       </c>
       <c r="I4" s="6"/>
     </row>
-    <row r="5" spans="1:9" ht="74.25" customHeight="1">
-      <c r="A5" s="41"/>
+    <row r="5" spans="1:9" ht="64.5" customHeight="1">
+      <c r="A5" s="39"/>
       <c r="B5" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D5" s="60" t="s">
+      <c r="D5" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E5" s="31" t="s">
+      <c r="E5" s="43" t="s">
         <v>20</v>
       </c>
-      <c r="F5" s="29" t="s">
+      <c r="F5" s="5" t="s">
         <v>21</v>
       </c>
       <c r="G5" s="5" t="s">
@@ -1399,775 +1375,771 @@
       </c>
       <c r="I5" s="6"/>
     </row>
-    <row r="6" spans="1:9" ht="74.25" customHeight="1">
-      <c r="A6" s="41"/>
+    <row r="6" spans="1:9" ht="64.5" customHeight="1">
+      <c r="A6" s="39"/>
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="60" t="s">
+      <c r="D6" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E6" s="30" t="s">
+      <c r="E6" s="39"/>
+      <c r="F6" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="F6" s="29" t="s">
+      <c r="G6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G6" s="5" t="s">
-        <v>22</v>
-      </c>
       <c r="H6" s="17" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="64.5" customHeight="1">
-      <c r="A7" s="41"/>
+    <row r="7" spans="1:9" ht="56.25" customHeight="1">
+      <c r="A7" s="44"/>
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="D7" s="60" t="s">
+      <c r="D7" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E7" s="40" t="s">
+      <c r="E7" s="39"/>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="G7" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="45" customHeight="1">
+      <c r="A8" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="G7" s="5" t="s">
+      <c r="B8" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="H7" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" ht="45" customHeight="1">
-      <c r="A8" s="45" t="s">
+      <c r="C8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="E8" s="39"/>
+      <c r="F8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="60" t="s">
+      <c r="G8" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="E8" s="40"/>
-      <c r="F8" s="29" t="s">
+      <c r="H8" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="76.5" customHeight="1">
+      <c r="A9" s="38"/>
+      <c r="B9" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="D9" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" ht="76.5" customHeight="1">
-      <c r="A9" s="41"/>
-      <c r="B9" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C9" s="5" t="s">
+      <c r="E9" s="39"/>
+      <c r="F9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D9" s="60" t="s">
+      <c r="G9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="40"/>
-      <c r="F9" s="29" t="s">
+      <c r="H9" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I9" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G9" s="5" t="s">
+    </row>
+    <row r="10" spans="1:9" s="1" customFormat="1" ht="62.25" customHeight="1">
+      <c r="A10" s="38"/>
+      <c r="B10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="H9" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="D10" s="3" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" s="1" customFormat="1" ht="62.25" customHeight="1">
-      <c r="A10" s="41"/>
-      <c r="B10" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="E10" s="39"/>
+      <c r="F10" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="61" t="s">
+      <c r="G10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="40"/>
-      <c r="F10" s="13" t="s">
+      <c r="H10" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:9" s="1" customFormat="1" ht="62.25" customHeight="1">
+      <c r="A11" s="38"/>
+      <c r="B11" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="D11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="H10" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I10" s="4"/>
-    </row>
-    <row r="11" spans="1:9" s="1" customFormat="1" ht="62.25" customHeight="1">
-      <c r="A11" s="41"/>
-      <c r="B11" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="E11" s="39"/>
+      <c r="F11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H11" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:9" s="1" customFormat="1" ht="43.5" customHeight="1">
+      <c r="A12" s="38"/>
+      <c r="B12" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C12" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="D11" s="61" t="s">
+      <c r="D12" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="E11" s="40"/>
-      <c r="F11" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H11" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I11" s="4"/>
-    </row>
-    <row r="12" spans="1:9" s="1" customFormat="1" ht="43.5" customHeight="1">
-      <c r="A12" s="41"/>
-      <c r="B12" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12" s="3" t="s">
+      <c r="E12" s="39"/>
+      <c r="F12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="D12" s="61" t="s">
+      <c r="G12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="13" t="s">
+      <c r="H12" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="I12" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="H12" s="18" t="s">
+    </row>
+    <row r="13" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1">
-      <c r="A13" s="41"/>
-      <c r="B13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="E13" s="39"/>
+      <c r="F13" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H13" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:9" s="1" customFormat="1" ht="82.5" customHeight="1">
+      <c r="A14" s="38"/>
+      <c r="B14" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="D13" s="60" t="s">
+      <c r="D14" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E13" s="40"/>
-      <c r="F13" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H13" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I13" s="4"/>
-    </row>
-    <row r="14" spans="1:9" s="1" customFormat="1" ht="82.5" customHeight="1">
-      <c r="A14" s="41"/>
-      <c r="B14" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C14" s="5" t="s">
+      <c r="E14" s="39"/>
+      <c r="F14" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H14" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="1" customFormat="1" ht="63.75" customHeight="1">
+      <c r="A15" s="38"/>
+      <c r="B15" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D14" s="60" t="s">
+      <c r="D15" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="E14" s="40"/>
-      <c r="F14" s="29" t="s">
+      <c r="E15" s="39"/>
+      <c r="F15" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H15" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="4"/>
+    </row>
+    <row r="16" spans="1:9" s="1" customFormat="1" ht="63.75" customHeight="1">
+      <c r="A16" s="38"/>
+      <c r="B16" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" s="39"/>
+      <c r="F16" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H16" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="4"/>
+    </row>
+    <row r="17" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1">
+      <c r="A17" s="38"/>
+      <c r="B17" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="39"/>
+      <c r="F17" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="H17" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I17" s="24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1">
+      <c r="A18" s="38"/>
+      <c r="B18" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="39"/>
+      <c r="F18" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="G18" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="H18" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="4"/>
+    </row>
+    <row r="19" spans="1:9" s="1" customFormat="1" ht="78.75" customHeight="1">
+      <c r="A19" s="38"/>
+      <c r="B19" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="E19" s="39"/>
+      <c r="F19" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="G19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="H19" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="G14" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H14" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I14" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="1" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A15" s="41"/>
-      <c r="B15" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="61" t="s">
-        <v>61</v>
-      </c>
-      <c r="E15" s="40"/>
-      <c r="F15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G15" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H15" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I15" s="4"/>
-    </row>
-    <row r="16" spans="1:9" s="1" customFormat="1" ht="63.75" customHeight="1">
-      <c r="A16" s="41"/>
-      <c r="B16" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D16" s="61" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" s="40"/>
-      <c r="F16" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H16" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="4"/>
-    </row>
-    <row r="17" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1">
-      <c r="A17" s="41"/>
-      <c r="B17" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D17" s="61" t="s">
+    </row>
+    <row r="20" spans="1:9" s="1" customFormat="1" ht="60" customHeight="1">
+      <c r="A20" s="38"/>
+      <c r="B20" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E17" s="40"/>
-      <c r="F17" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="H17" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="1" customFormat="1" ht="47.25" customHeight="1">
-      <c r="A18" s="41"/>
-      <c r="B18" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C18" s="6" t="s">
-        <v>69</v>
-      </c>
-      <c r="D18" s="60" t="s">
-        <v>70</v>
-      </c>
-      <c r="E18" s="40"/>
-      <c r="F18" s="29" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="H18" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I18" s="4"/>
-    </row>
-    <row r="19" spans="1:9" s="1" customFormat="1" ht="78.75" customHeight="1">
-      <c r="A19" s="41"/>
-      <c r="B19" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="C19" s="5" t="s">
+      <c r="C20" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D19" s="60" t="s">
+      <c r="D20" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="E19" s="40"/>
-      <c r="F19" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="G19" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="H19" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I19" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" s="1" customFormat="1" ht="60" customHeight="1">
-      <c r="A20" s="41"/>
-      <c r="B20" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="3" t="s">
+      <c r="E20" s="39"/>
+      <c r="F20" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="H20" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="4"/>
+    </row>
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="57" customHeight="1">
+      <c r="A21" s="38"/>
+      <c r="B21" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D20" s="61" t="s">
+      <c r="D21" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="40"/>
-      <c r="F20" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="H20" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I20" s="4"/>
-    </row>
-    <row r="21" spans="1:9" s="1" customFormat="1" ht="57" customHeight="1">
-      <c r="A21" s="41"/>
-      <c r="B21" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D21" s="61" t="s">
-        <v>76</v>
-      </c>
-      <c r="E21" s="40"/>
-      <c r="F21" s="13" t="s">
-        <v>45</v>
+      <c r="E21" s="39"/>
+      <c r="F21" s="3" t="s">
+        <v>43</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H21" s="17"/>
       <c r="I21" s="4"/>
     </row>
     <row r="22" spans="1:9" s="1" customFormat="1" ht="45.75" customHeight="1">
-      <c r="A22" s="46"/>
+      <c r="A22" s="38"/>
       <c r="B22" s="11" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="E22" s="44"/>
+      <c r="F22" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G22" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D22" s="61" t="s">
+      <c r="H22" s="18" t="s">
+        <v>51</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" ht="33.75" customHeight="1">
+      <c r="A23" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="E22" s="40"/>
-      <c r="F22" s="29" t="s">
+      <c r="B23" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="35" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="39" t="s">
+        <v>82</v>
+      </c>
+      <c r="F23" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="G23" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="8"/>
+    </row>
+    <row r="24" spans="1:9" ht="29.25">
+      <c r="A24" s="45"/>
+      <c r="B24" s="38"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" s="39"/>
+      <c r="F24" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="18" t="s">
         <v>51</v>
       </c>
-      <c r="G22" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="H22" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="33.75" customHeight="1">
-      <c r="A23" s="47" t="s">
-        <v>80</v>
-      </c>
-      <c r="B23" s="40" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" s="37" t="s">
-        <v>82</v>
-      </c>
-      <c r="D23" s="19" t="s">
-        <v>83</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="F23" s="19" t="s">
-        <v>85</v>
-      </c>
-      <c r="G23" s="19" t="s">
-        <v>86</v>
-      </c>
-      <c r="H23" s="23" t="s">
-        <v>17</v>
-      </c>
-      <c r="I23" s="8"/>
-    </row>
-    <row r="24" spans="1:9" ht="29.25">
-      <c r="A24" s="47"/>
-      <c r="B24" s="40"/>
-      <c r="C24" s="38"/>
-      <c r="D24" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E24" s="41"/>
-      <c r="F24" s="3" t="s">
+      <c r="I24" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="G24" s="3" t="s">
+    </row>
+    <row r="25" spans="1:9" ht="39" customHeight="1">
+      <c r="A25" s="45"/>
+      <c r="B25" s="38"/>
+      <c r="C25" s="37" t="s">
         <v>89</v>
       </c>
-      <c r="H24" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="I24" s="8" t="s">
+      <c r="D25" s="9" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="39" customHeight="1">
-      <c r="A25" s="47"/>
-      <c r="B25" s="40"/>
-      <c r="C25" s="39" t="s">
+      <c r="E25" s="39"/>
+      <c r="F25" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D25" s="9" t="s">
+      <c r="G25" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E25" s="41"/>
-      <c r="F25" s="10" t="s">
+      <c r="H25" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="8"/>
+    </row>
+    <row r="26" spans="1:9" ht="46.5" customHeight="1">
+      <c r="A26" s="45"/>
+      <c r="B26" s="38"/>
+      <c r="C26" s="37"/>
+      <c r="D26" s="9" t="s">
         <v>93</v>
       </c>
-      <c r="G25" s="3" t="s">
+      <c r="E26" s="39"/>
+      <c r="F26" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="H25" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I25" s="8"/>
-    </row>
-    <row r="26" spans="1:9" ht="46.5" customHeight="1">
-      <c r="A26" s="47"/>
-      <c r="B26" s="40"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="9" t="s">
+      <c r="G26" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E26" s="41"/>
-      <c r="F26" s="10" t="s">
+      <c r="H26" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="8"/>
+    </row>
+    <row r="27" spans="1:9" ht="34.5" customHeight="1">
+      <c r="A27" s="45"/>
+      <c r="B27" s="38"/>
+      <c r="C27" s="26" t="s">
         <v>96</v>
       </c>
-      <c r="G26" s="3" t="s">
+      <c r="D27" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="H26" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I26" s="8"/>
-    </row>
-    <row r="27" spans="1:9" ht="34.5" customHeight="1">
-      <c r="A27" s="47"/>
-      <c r="B27" s="40"/>
-      <c r="C27" s="26" t="s">
+      <c r="E27" s="39"/>
+      <c r="F27" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="D27" s="9" t="s">
+      <c r="G27" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E27" s="41"/>
-      <c r="F27" s="12" t="s">
+      <c r="H27" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I27" s="8"/>
+    </row>
+    <row r="28" spans="1:9" ht="34.5" customHeight="1">
+      <c r="A28" s="45"/>
+      <c r="B28" s="38"/>
+      <c r="C28" s="26" t="s">
         <v>100</v>
       </c>
-      <c r="G27" s="3" t="s">
+      <c r="D28" s="9" t="s">
         <v>101</v>
       </c>
-      <c r="H27" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I27" s="8"/>
-    </row>
-    <row r="28" spans="1:9" ht="34.5" customHeight="1">
-      <c r="A28" s="47"/>
-      <c r="B28" s="40"/>
-      <c r="C28" s="26" t="s">
+      <c r="E28" s="40"/>
+      <c r="F28" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="D28" s="9" t="s">
+      <c r="G28" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="E28" s="42"/>
-      <c r="F28" s="10" t="s">
+      <c r="H28" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I28" s="8"/>
+    </row>
+    <row r="29" spans="1:9" ht="43.5" customHeight="1">
+      <c r="A29" s="45"/>
+      <c r="B29" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="G28" s="13" t="s">
+      <c r="C29" s="26" t="s">
         <v>105</v>
       </c>
-      <c r="H28" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I28" s="8"/>
-    </row>
-    <row r="29" spans="1:9" ht="43.5" customHeight="1">
-      <c r="A29" s="47"/>
-      <c r="B29" s="32" t="s">
+      <c r="D29" s="9" t="s">
         <v>106</v>
       </c>
-      <c r="C29" s="26" t="s">
+      <c r="E29" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="D29" s="9" t="s">
+      <c r="F29" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="G29" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="F29" s="10" t="s">
+      <c r="H29" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I29" s="8"/>
+    </row>
+    <row r="30" spans="1:9" ht="29.25">
+      <c r="A30" s="45"/>
+      <c r="B30" s="30"/>
+      <c r="C30" s="20" t="s">
         <v>110</v>
       </c>
-      <c r="G29" s="20" t="s">
+      <c r="D30" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="H29" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I29" s="8"/>
-    </row>
-    <row r="30" spans="1:9" ht="29.25">
-      <c r="A30" s="47"/>
-      <c r="B30" s="32"/>
-      <c r="C30" s="20" t="s">
+      <c r="E30" s="42"/>
+      <c r="F30" s="14" t="s">
         <v>112</v>
       </c>
-      <c r="D30" s="3" t="s">
+      <c r="G30" s="13" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="44"/>
-      <c r="F30" s="14" t="s">
+      <c r="H30" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I30" s="8"/>
+    </row>
+    <row r="31" spans="1:9" ht="29.25">
+      <c r="A31" s="45"/>
+      <c r="B31" s="30"/>
+      <c r="C31" s="27" t="s">
         <v>114</v>
       </c>
-      <c r="G30" s="13" t="s">
+      <c r="D31" s="11" t="s">
         <v>115</v>
       </c>
-      <c r="H30" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I30" s="8"/>
-    </row>
-    <row r="31" spans="1:9" ht="29.25">
-      <c r="A31" s="47"/>
-      <c r="B31" s="32"/>
-      <c r="C31" s="27" t="s">
+      <c r="E31" s="40"/>
+      <c r="F31" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D31" s="11" t="s">
+      <c r="G31" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="E31" s="42"/>
-      <c r="F31" s="15" t="s">
+      <c r="H31" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" ht="29.25">
+      <c r="A32" s="46"/>
+      <c r="B32" s="31" t="s">
         <v>118</v>
       </c>
-      <c r="G31" s="3" t="s">
+      <c r="C32" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="H31" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I31" s="8"/>
-    </row>
-    <row r="32" spans="1:9" ht="29.25">
-      <c r="A32" s="48"/>
-      <c r="B32" s="33" t="s">
+      <c r="D32" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C32" s="10" t="s">
+      <c r="E32" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="F32" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="G32" s="13" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="3" t="s">
+      <c r="H32" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:9" ht="29.25">
+      <c r="A33" s="46"/>
+      <c r="B33" s="31"/>
+      <c r="C33" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="G32" s="13" t="s">
+      <c r="D33" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H32" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I32" s="8"/>
-    </row>
-    <row r="33" spans="1:9" ht="29.25">
-      <c r="A33" s="48"/>
-      <c r="B33" s="33"/>
-      <c r="C33" s="7" t="s">
+      <c r="E33" s="39"/>
+      <c r="F33" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="G33" s="13" t="s">
         <v>127</v>
       </c>
-      <c r="E33" s="41"/>
-      <c r="F33" s="10" t="s">
+      <c r="H33" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9" ht="29.25">
+      <c r="A34" s="47"/>
+      <c r="B34" s="32"/>
+      <c r="C34" s="16" t="s">
         <v>128</v>
       </c>
-      <c r="G33" s="13" t="s">
+      <c r="D34" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="44"/>
+      <c r="F34" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="H33" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I33" s="8"/>
-    </row>
-    <row r="34" spans="1:9" ht="29.25">
-      <c r="A34" s="49"/>
-      <c r="B34" s="34"/>
-      <c r="C34" s="16" t="s">
+      <c r="G34" s="13" t="s">
+        <v>117</v>
+      </c>
+      <c r="H34" s="17" t="s">
+        <v>17</v>
+      </c>
+      <c r="I34" s="8"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="48" t="s">
         <v>130</v>
       </c>
-      <c r="D34" s="7" t="s">
+      <c r="B35" s="49"/>
+      <c r="C35" s="49"/>
+      <c r="D35" s="49"/>
+      <c r="E35" s="49"/>
+      <c r="F35" s="49"/>
+      <c r="G35" s="49"/>
+      <c r="H35" s="49"/>
+      <c r="I35" s="50"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" s="51"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
+      <c r="D36" s="52"/>
+      <c r="E36" s="52"/>
+      <c r="F36" s="52"/>
+      <c r="G36" s="52"/>
+      <c r="H36" s="52"/>
+      <c r="I36" s="50"/>
+    </row>
+    <row r="37" spans="1:9" s="21" customFormat="1">
+      <c r="A37" s="53" t="s">
         <v>131</v>
       </c>
-      <c r="E34" s="46"/>
-      <c r="F34" s="3" t="s">
+      <c r="B37" s="53"/>
+      <c r="C37" s="53"/>
+      <c r="D37" s="53"/>
+      <c r="E37" s="53" t="s">
         <v>132</v>
       </c>
-      <c r="G34" s="13" t="s">
-        <v>119</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="I34" s="8"/>
-    </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="50" t="s">
+      <c r="F37" s="53"/>
+      <c r="G37" s="53"/>
+      <c r="H37" s="53"/>
+      <c r="I37" s="53"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" s="54" t="s">
         <v>133</v>
       </c>
-      <c r="B35" s="51"/>
-      <c r="C35" s="51"/>
-      <c r="D35" s="51"/>
-      <c r="E35" s="51"/>
-      <c r="F35" s="51"/>
-      <c r="G35" s="51"/>
-      <c r="H35" s="51"/>
-      <c r="I35" s="52"/>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="53"/>
-      <c r="B36" s="54"/>
-      <c r="C36" s="54"/>
-      <c r="D36" s="54"/>
-      <c r="E36" s="54"/>
-      <c r="F36" s="54"/>
-      <c r="G36" s="54"/>
-      <c r="H36" s="54"/>
-      <c r="I36" s="52"/>
-    </row>
-    <row r="37" spans="1:9" s="21" customFormat="1">
-      <c r="A37" s="55" t="s">
+      <c r="B38" s="55"/>
+      <c r="C38" s="55"/>
+      <c r="D38" s="56"/>
+      <c r="E38" s="54">
+        <v>29</v>
+      </c>
+      <c r="F38" s="55"/>
+      <c r="G38" s="55"/>
+      <c r="H38" s="55"/>
+      <c r="I38" s="56"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" s="54" t="s">
         <v>134</v>
       </c>
-      <c r="B37" s="55"/>
-      <c r="C37" s="55"/>
-      <c r="D37" s="55"/>
-      <c r="E37" s="55" t="s">
+      <c r="B39" s="55"/>
+      <c r="C39" s="55"/>
+      <c r="D39" s="56"/>
+      <c r="E39" s="54">
+        <v>4</v>
+      </c>
+      <c r="F39" s="55"/>
+      <c r="G39" s="55"/>
+      <c r="H39" s="55"/>
+      <c r="I39" s="56"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" s="54" t="s">
         <v>135</v>
       </c>
-      <c r="F37" s="55"/>
-      <c r="G37" s="55"/>
-      <c r="H37" s="55"/>
-      <c r="I37" s="55"/>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="56" t="s">
+      <c r="B40" s="55"/>
+      <c r="C40" s="55"/>
+      <c r="D40" s="56"/>
+      <c r="E40" s="57">
+        <v>0.878</v>
+      </c>
+      <c r="F40" s="55"/>
+      <c r="G40" s="55"/>
+      <c r="H40" s="55"/>
+      <c r="I40" s="56"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="54" t="s">
         <v>136</v>
       </c>
-      <c r="B38" s="57"/>
-      <c r="C38" s="57"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="56">
-        <v>30</v>
-      </c>
-      <c r="F38" s="57"/>
-      <c r="G38" s="57"/>
-      <c r="H38" s="57"/>
-      <c r="I38" s="58"/>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="56" t="s">
-        <v>137</v>
-      </c>
-      <c r="B39" s="57"/>
-      <c r="C39" s="57"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="56">
-        <v>4</v>
-      </c>
-      <c r="F39" s="57"/>
-      <c r="G39" s="57"/>
-      <c r="H39" s="57"/>
-      <c r="I39" s="58"/>
-    </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="56" t="s">
-        <v>138</v>
-      </c>
-      <c r="B40" s="57"/>
-      <c r="C40" s="57"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="59">
-        <v>0.878</v>
-      </c>
-      <c r="F40" s="57"/>
-      <c r="G40" s="57"/>
-      <c r="H40" s="57"/>
-      <c r="I40" s="58"/>
-    </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="56" t="s">
-        <v>139</v>
-      </c>
-      <c r="B41" s="57"/>
-      <c r="C41" s="57"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="59">
+      <c r="B41" s="55"/>
+      <c r="C41" s="55"/>
+      <c r="D41" s="56"/>
+      <c r="E41" s="57">
         <v>0.12</v>
       </c>
-      <c r="F41" s="57"/>
-      <c r="G41" s="57"/>
-      <c r="H41" s="57"/>
-      <c r="I41" s="58"/>
+      <c r="F41" s="55"/>
+      <c r="G41" s="55"/>
+      <c r="H41" s="55"/>
+      <c r="I41" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -2194,7 +2166,7 @@
     <mergeCell ref="A23:A34"/>
     <mergeCell ref="A8:A22"/>
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="E7:E22"/>
+    <mergeCell ref="E5:E22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Assignmnet-1/testplan.xlsx
+++ b/Assignmnet-1/testplan.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29108"/>
   <workbookPr/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{26DAB415-8564-4565-98A4-D4CD7DCB3EC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3CF92AD2-D790-4454-B444-DD1290CD0A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1398,7 +1398,7 @@
       </c>
       <c r="I6" s="6"/>
     </row>
-    <row r="7" spans="1:9" ht="56.25" customHeight="1">
+    <row r="7" spans="1:9" ht="66" customHeight="1">
       <c r="A7" s="44"/>
       <c r="B7" s="5" t="s">
         <v>11</v>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I20" s="4"/>
     </row>
-    <row r="21" spans="1:9" s="1" customFormat="1" ht="57" customHeight="1">
+    <row r="21" spans="1:9" s="1" customFormat="1" ht="62.25" customHeight="1">
       <c r="A21" s="38"/>
       <c r="B21" s="3" t="s">
         <v>66</v>
@@ -2089,7 +2089,7 @@
       <c r="C38" s="55"/>
       <c r="D38" s="56"/>
       <c r="E38" s="54">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F38" s="55"/>
       <c r="G38" s="55"/>
